--- a/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren</t>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,42; 75,85</t>
+          <t>61,2; 76,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,43; 94,33</t>
+          <t>83,3; 94,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,28; 78,75</t>
+          <t>62,81; 78,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,18; 40,53</t>
+          <t>26,91; 40,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,78; 79,17</t>
+          <t>65,19; 78,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,93; 89,84</t>
+          <t>78,88; 90,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,12; 83,88</t>
+          <t>70,89; 84,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,44; 52,72</t>
+          <t>28,25; 50,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65,56; 75,74</t>
+          <t>66,22; 75,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83,01; 90,85</t>
+          <t>83,22; 91,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,71; 79,74</t>
+          <t>69,17; 79,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,71; 43,8</t>
+          <t>29,57; 44,91</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,78; 77,51</t>
+          <t>64,46; 76,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,29; 94,51</t>
+          <t>86,45; 94,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,42; 79,58</t>
+          <t>68,48; 80,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,73; 45,43</t>
+          <t>31,87; 45,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,61; 78,53</t>
+          <t>66,1; 78,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,62; 90,69</t>
+          <t>81,74; 90,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,18; 85,1</t>
+          <t>75,24; 84,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,04; 48,86</t>
+          <t>36,45; 48,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67,36; 76,19</t>
+          <t>67,33; 76,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85,32; 91,38</t>
+          <t>85,14; 91,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73,93; 81,13</t>
+          <t>73,88; 81,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,24; 45,2</t>
+          <t>36,07; 44,94</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,47; 71,61</t>
+          <t>57,96; 71,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,04; 93,42</t>
+          <t>83,68; 93,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,62; 77,56</t>
+          <t>63,71; 76,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 25,45</t>
+          <t>12,4; 25,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,18; 72,34</t>
+          <t>58,6; 72,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,13; 94,62</t>
+          <t>86,59; 94,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,81; 77,59</t>
+          <t>64,27; 77,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,64; 25,0</t>
+          <t>14,9; 26,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60,65; 69,91</t>
+          <t>59,3; 69,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87,06; 92,97</t>
+          <t>86,69; 93,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,32; 75,89</t>
+          <t>66,41; 75,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 23,65</t>
+          <t>14,49; 23,55</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,82; 78,29</t>
+          <t>66,06; 77,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,57; 93,29</t>
+          <t>84,71; 93,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,8; 79,19</t>
+          <t>67,67; 80,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,47; 36,27</t>
+          <t>23,5; 35,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,23; 71,09</t>
+          <t>58,38; 70,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,58; 92,81</t>
+          <t>83,61; 92,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,96; 77,7</t>
+          <t>65,56; 78,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,32; 35,31</t>
+          <t>23,46; 35,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,55; 72,15</t>
+          <t>64,04; 73,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85,75; 91,74</t>
+          <t>85,82; 91,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,46; 76,78</t>
+          <t>68,84; 76,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,3; 33,69</t>
+          <t>25,2; 33,48</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,16; 72,69</t>
+          <t>66,23; 72,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,35; 91,87</t>
+          <t>87,45; 92,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,78; 76,16</t>
+          <t>69,63; 76,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,08; 33,2</t>
+          <t>25,46; 33,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,3; 71,81</t>
+          <t>65,58; 72,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,42; 89,91</t>
+          <t>85,3; 90,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,78; 78,78</t>
+          <t>72,74; 78,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,57; 36,88</t>
+          <t>29,85; 36,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67,07; 71,51</t>
+          <t>67,03; 71,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,28; 90,51</t>
+          <t>87,12; 90,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,2; 76,7</t>
+          <t>72,33; 76,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,78; 33,89</t>
+          <t>28,77; 34,44</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>72947</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>87401</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>63948</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39156</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95670</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81723</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>52341</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>159074</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>183070</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>145672</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>91497</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>64388; 80377</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80909; 91678</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56586; 70615</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>31565; 46952</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>77117; 93203</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>88741; 101445</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>74200; 88222</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>39671; 71595</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>148002; 169584</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>174461; 191078</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>134709; 154738</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>76203; 115727</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>88676</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>117117</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>113491</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72092</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>102019</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>134319</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>140807</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>108746</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>190695</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>251436</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>254299</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>180838</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>80552; 96068</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111510; 121499</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>104041; 122116</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>60714; 87501</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>93035; 109920</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>126340; 139891</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>131901; 148347</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>92952; 122903</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>178890; 202287</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>241397; 258837</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>241756; 265694</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>160690; 200224</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>69834</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>93772</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82684</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37089</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73793</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>106272</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95183</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>36690</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>143627</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>200043</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>177867</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>73779</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>62510; 77509</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87743; 97749</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74249; 89567</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23612; 48858</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>65964; 82010</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>101126; 110602</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>85378; 103047</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>27600; 48967</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>130719; 154203</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>192142; 206300</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>165626; 188993</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>54429; 88487</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>119272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>130649</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>123519</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49456</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>101883</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>137386</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>114135</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>53267</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>221156</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>268035</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>237654</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>102724</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>109216; 128277</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>123678; 136673</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>112889; 133498</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39463; 59820</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>91629; 111255</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>129544; 143161</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>103716; 123478</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>42525; 64634</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>206375; 235602</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>258256; 275911</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>223764; 250104</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>87997; 116914</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>350731</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>428939</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>383642</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>197792</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>251045</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>714551</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>902584</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>815492</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>448837</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>333400; 366650</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>417091; 439171</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>365828; 399645</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>169597; 221165</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>346609; 381488</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>459598; 485395</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>415346; 448830</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>227448; 279996</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>691673; 741191</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>884960; 917749</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>792992; 837837</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>410914; 491807</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61,2; 76,4</t>
+          <t>62,03; 76,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,3; 94,39</t>
+          <t>83,92; 94,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,81; 78,39</t>
+          <t>62,1; 78,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,91; 40,03</t>
+          <t>26,7; 40,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,19; 78,79</t>
+          <t>65,9; 79,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,88; 90,17</t>
+          <t>78,61; 89,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,89; 84,28</t>
+          <t>70,47; 84,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,25; 50,99</t>
+          <t>27,75; 52,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,22; 75,88</t>
+          <t>66,16; 76,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83,22; 91,15</t>
+          <t>82,98; 90,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69,17; 79,45</t>
+          <t>69,52; 80,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,57; 44,91</t>
+          <t>29,69; 44,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,46; 76,88</t>
+          <t>64,36; 76,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,45; 94,2</t>
+          <t>86,17; 94,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,48; 80,38</t>
+          <t>69,23; 79,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,87; 45,93</t>
+          <t>31,31; 45,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,1; 78,1</t>
+          <t>65,84; 77,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,74; 90,51</t>
+          <t>82,36; 90,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,24; 84,62</t>
+          <t>75,5; 84,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>36,45; 48,19</t>
+          <t>37,14; 48,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67,33; 76,13</t>
+          <t>67,53; 75,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85,14; 91,29</t>
+          <t>85,59; 91,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73,88; 81,19</t>
+          <t>74,08; 81,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,07; 44,94</t>
+          <t>36,17; 45,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,96; 71,87</t>
+          <t>57,59; 71,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,68; 93,23</t>
+          <t>84,3; 93,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,71; 76,85</t>
+          <t>64,15; 77,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,4; 25,66</t>
+          <t>11,25; 26,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,6; 72,85</t>
+          <t>58,63; 72,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,59; 94,71</t>
+          <t>86,21; 94,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,27; 77,57</t>
+          <t>64,76; 78,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 26,43</t>
+          <t>14,88; 24,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,3; 69,96</t>
+          <t>60,01; 69,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86,69; 93,08</t>
+          <t>86,95; 93,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,41; 75,78</t>
+          <t>66,61; 75,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,49; 23,55</t>
+          <t>14,63; 23,78</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,06; 77,59</t>
+          <t>66,36; 77,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,71; 93,61</t>
+          <t>85,03; 93,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,67; 80,02</t>
+          <t>67,38; 79,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,5; 35,62</t>
+          <t>23,97; 35,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,38; 70,89</t>
+          <t>58,43; 70,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,61; 92,4</t>
+          <t>83,53; 92,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,56; 78,05</t>
+          <t>66,07; 77,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,46; 35,66</t>
+          <t>24,1; 36,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,04; 73,1</t>
+          <t>64,29; 72,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85,82; 91,68</t>
+          <t>85,72; 91,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,84; 76,95</t>
+          <t>68,67; 77,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,2; 33,48</t>
+          <t>25,56; 33,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,84</t>
+          <t>66,48; 72,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,45; 92,08</t>
+          <t>87,71; 91,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,63; 76,07</t>
+          <t>69,96; 76,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,46; 33,2</t>
+          <t>25,47; 33,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,58; 72,18</t>
+          <t>65,6; 72,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,3; 90,09</t>
+          <t>85,66; 90,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,74; 78,6</t>
+          <t>72,45; 78,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,85; 36,75</t>
+          <t>29,46; 37,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67,03; 71,83</t>
+          <t>66,82; 71,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,12; 90,35</t>
+          <t>87,09; 90,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,33; 76,42</t>
+          <t>72,17; 76,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,77; 34,44</t>
+          <t>28,7; 33,82</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>64388; 80377</t>
+          <t>65266; 80504</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>80909; 91678</t>
+          <t>81512; 91870</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56586; 70615</t>
+          <t>55941; 70654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31565; 46952</t>
+          <t>31313; 47788</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77117; 93203</t>
+          <t>77950; 93671</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88741; 101445</t>
+          <t>88433; 101174</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74200; 88222</t>
+          <t>73768; 88430</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39671; 71595</t>
+          <t>38963; 73792</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>148002; 169584</t>
+          <t>147863; 170128</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>174461; 191078</t>
+          <t>173956; 190053</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134709; 154738</t>
+          <t>135395; 156138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76203; 115727</t>
+          <t>76519; 115002</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80552; 96068</t>
+          <t>80427; 95870</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111510; 121499</t>
+          <t>111145; 121603</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104041; 122116</t>
+          <t>105178; 121531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60714; 87501</t>
+          <t>59655; 86519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93035; 109920</t>
+          <t>92660; 109383</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>126340; 139891</t>
+          <t>127289; 140427</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>131901; 148347</t>
+          <t>132356; 148581</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92952; 122903</t>
+          <t>94729; 124008</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178890; 202287</t>
+          <t>179419; 201641</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>241397; 258837</t>
+          <t>242689; 259344</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>241756; 265694</t>
+          <t>242427; 266191</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>160690; 200224</t>
+          <t>161138; 200747</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62510; 77509</t>
+          <t>62105; 77568</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87743; 97749</t>
+          <t>88393; 97948</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74249; 89567</t>
+          <t>74765; 89791</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23612; 48858</t>
+          <t>21412; 49815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>65964; 82010</t>
+          <t>66000; 81457</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>101126; 110602</t>
+          <t>100681; 110350</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85378; 103047</t>
+          <t>86028; 104133</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27600; 48967</t>
+          <t>27570; 46263</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>130719; 154203</t>
+          <t>132268; 152877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>192142; 206300</t>
+          <t>192712; 206198</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165626; 188993</t>
+          <t>166120; 189454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54429; 88487</t>
+          <t>54950; 89348</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>109216; 128277</t>
+          <t>109719; 128820</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>123678; 136673</t>
+          <t>124140; 136346</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112889; 133498</t>
+          <t>112404; 133289</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39463; 59820</t>
+          <t>40258; 60436</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91629; 111255</t>
+          <t>91700; 111354</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>129544; 143161</t>
+          <t>129424; 143407</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>103716; 123478</t>
+          <t>104534; 123162</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42525; 64634</t>
+          <t>43680; 65300</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>206375; 235602</t>
+          <t>207207; 235200</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>258256; 275911</t>
+          <t>257957; 276772</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>223764; 250104</t>
+          <t>223195; 250392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>87997; 116914</t>
+          <t>89261; 117653</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>333400; 366650</t>
+          <t>334656; 367316</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>417091; 439171</t>
+          <t>418324; 438557</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>365828; 399645</t>
+          <t>367557; 401043</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169597; 221165</t>
+          <t>169639; 220990</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>346609; 381488</t>
+          <t>346730; 380608</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>459598; 485395</t>
+          <t>461494; 486339</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>415346; 448830</t>
+          <t>413730; 448105</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>227448; 279996</t>
+          <t>224471; 283042</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>691673; 741191</t>
+          <t>689538; 738597</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>884960; 917749</t>
+          <t>884572; 918467</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>792992; 837837</t>
+          <t>791295; 838073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>410914; 491807</t>
+          <t>409924; 482981</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>85,04%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78,07%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>69,34%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>89,98%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>70,99%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33,39%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>72,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>85,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,07%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,03; 76,52</t>
+          <t>65,78; 79,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,92; 94,59</t>
+          <t>77,93; 89,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,1; 78,43</t>
+          <t>70,12; 83,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 40,75</t>
+          <t>29,96; 52,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,9; 79,19</t>
+          <t>61,42; 75,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,61; 89,93</t>
+          <t>83,43; 94,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,47; 84,48</t>
+          <t>62,28; 78,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,75; 52,55</t>
+          <t>26,95; 40,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,16; 76,12</t>
+          <t>65,56; 75,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82,98; 90,66</t>
+          <t>83,01; 90,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69,52; 80,17</t>
+          <t>68,71; 79,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,69; 44,63</t>
+          <t>30,42; 42,98</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>72,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86,91%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43,69%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>70,96%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>90,8%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>74,7%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>72,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>86,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,36; 76,72</t>
+          <t>66,61; 78,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,17; 94,28</t>
+          <t>81,62; 90,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,23; 79,99</t>
+          <t>75,18; 85,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,31; 45,41</t>
+          <t>37,69; 50,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,84; 77,72</t>
+          <t>64,78; 77,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,36; 90,86</t>
+          <t>86,29; 94,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,5; 84,76</t>
+          <t>68,42; 79,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,14; 48,62</t>
+          <t>30,65; 42,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67,53; 75,89</t>
+          <t>67,36; 76,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85,59; 91,47</t>
+          <t>85,32; 91,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74,08; 81,35</t>
+          <t>73,93; 81,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,17; 45,06</t>
+          <t>36,25; 44,72</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>65,55%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71,65%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20,48%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>64,75%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>89,43%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>70,94%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,65%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,59; 71,92</t>
+          <t>58,18; 72,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,3; 93,42</t>
+          <t>86,13; 94,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,15; 77,04</t>
+          <t>64,81; 77,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,25; 26,16</t>
+          <t>15,04; 26,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,63; 72,36</t>
+          <t>57,47; 71,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,21; 94,49</t>
+          <t>84,04; 93,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,76; 78,39</t>
+          <t>63,62; 77,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,88; 24,97</t>
+          <t>17,81; 29,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60,01; 69,36</t>
+          <t>60,65; 69,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86,95; 93,04</t>
+          <t>87,06; 92,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,61; 75,96</t>
+          <t>66,32; 75,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,63; 23,78</t>
+          <t>18,05; 26,26</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64,92%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88,67%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>72,14%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>89,48%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>74,04%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>64,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>88,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,14%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,36; 77,91</t>
+          <t>58,23; 71,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,03; 93,39</t>
+          <t>83,58; 92,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,38; 79,9</t>
+          <t>65,96; 77,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,97; 35,98</t>
+          <t>23,66; 36,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,43; 70,95</t>
+          <t>66,82; 78,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,53; 92,56</t>
+          <t>84,57; 93,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,07; 77,85</t>
+          <t>67,8; 79,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,1; 36,03</t>
+          <t>25,12; 37,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,29; 72,98</t>
+          <t>64,55; 72,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85,72; 91,97</t>
+          <t>85,75; 91,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,67; 77,04</t>
+          <t>68,46; 76,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,56; 33,69</t>
+          <t>25,76; 34,39</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>69,68%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>89,93%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,48; 72,97</t>
+          <t>65,3; 71,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,71; 91,95</t>
+          <t>85,42; 89,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69,96; 76,33</t>
+          <t>72,78; 78,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,47; 33,17</t>
+          <t>30,61; 37,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,6; 72,01</t>
+          <t>66,16; 72,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,66; 90,27</t>
+          <t>87,35; 91,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,45; 78,47</t>
+          <t>69,78; 76,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,46; 37,15</t>
+          <t>28,03; 34,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,82; 71,58</t>
+          <t>67,07; 71,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,09; 90,42</t>
+          <t>87,28; 90,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,17; 76,44</t>
+          <t>72,2; 76,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,7; 33,82</t>
+          <t>30,14; 34,7</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>95670</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>81723</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48536</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>72947</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>87401</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>63948</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39156</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>86126</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95670</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81723</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52341</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91497</t>
+          <t>88912</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>65266; 80504</t>
+          <t>77810; 93649</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>81512; 91870</t>
+          <t>87673; 101065</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55941; 70654</t>
+          <t>73396; 87804</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31313; 47788</t>
+          <t>37718; 66714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77950; 93671</t>
+          <t>64624; 79804</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88433; 101174</t>
+          <t>81033; 91623</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73768; 88430</t>
+          <t>56106; 70938</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38963; 73792</t>
+          <t>32633; 49186</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147863; 170128</t>
+          <t>146533; 169287</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>173956; 190053</t>
+          <t>174008; 190456</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135395; 156138</t>
+          <t>133828; 155305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76519; 115002</t>
+          <t>75132; 106161</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>103</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102019</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>134319</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>140807</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>103632</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>88676</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>117117</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>113491</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72092</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>102019</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>134319</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>140807</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>108746</t>
+          <t>67137</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>180838</t>
+          <t>170768</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80427; 95870</t>
+          <t>93745; 110520</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111145; 121603</t>
+          <t>126147; 140171</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105178; 121531</t>
+          <t>131788; 149185</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59655; 86519</t>
+          <t>89392; 118631</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92660; 109383</t>
+          <t>80952; 96865</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>127289; 140427</t>
+          <t>111293; 121904</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132356; 148581</t>
+          <t>103948; 120903</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94729; 124008</t>
+          <t>56519; 78971</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>179419; 201641</t>
+          <t>178982; 202437</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>242689; 259344</t>
+          <t>241914; 259109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>242427; 266191</t>
+          <t>241924; 265471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>161138; 200747</t>
+          <t>152822; 188536</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>143</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>73793</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>106272</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95183</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34469</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>69834</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>93772</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>82684</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37089</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>73793</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>106272</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95183</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36690</t>
+          <t>36998</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73779</t>
+          <t>71467</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62105; 77568</t>
+          <t>65494; 81435</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88393; 97948</t>
+          <t>100587; 110498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74765; 89791</t>
+          <t>86094; 103069</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21412; 49815</t>
+          <t>25318; 43955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>66000; 81457</t>
+          <t>61975; 77228</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>100681; 110350</t>
+          <t>88112; 97952</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86028; 104133</t>
+          <t>74145; 90397</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27570; 46263</t>
+          <t>27969; 46197</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132268; 152877</t>
+          <t>133683; 154097</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>192712; 206198</t>
+          <t>192955; 206048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166120; 189454</t>
+          <t>165407; 189275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54950; 89348</t>
+          <t>58730; 85438</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>169</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>101883</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137386</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>114135</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50730</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>119272</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>130649</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>123519</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>49456</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>101883</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>137386</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>114135</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53267</t>
+          <t>50471</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>102724</t>
+          <t>101201</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>109719; 128820</t>
+          <t>91390; 111566</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>124140; 136346</t>
+          <t>129493; 143796</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112404; 133289</t>
+          <t>104352; 122922</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40258; 60436</t>
+          <t>40077; 61049</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91700; 111354</t>
+          <t>110473; 129442</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>129424; 143407</t>
+          <t>123468; 136209</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>104534; 123162</t>
+          <t>113110; 132104</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43680; 65300</t>
+          <t>41989; 62505</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>207207; 235200</t>
+          <t>208030; 232520</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>257957; 276772</t>
+          <t>258070; 276089</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>223195; 250392</t>
+          <t>222522; 249555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89261; 117653</t>
+          <t>86678; 115734</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>589</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>295</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>237366</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>350731</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>428939</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>383642</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>197792</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>363821</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>473645</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>431850</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>251045</t>
+          <t>194981</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>448837</t>
+          <t>432348</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>334656; 367316</t>
+          <t>345138; 379567</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>418324; 438557</t>
+          <t>460235; 484394</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>367557; 401043</t>
+          <t>415584; 449887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169639; 220990</t>
+          <t>214504; 264437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>346730; 380608</t>
+          <t>333008; 365889</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>461494; 486339</t>
+          <t>416621; 438190</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>413730; 448105</t>
+          <t>366597; 400140</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>224471; 283042</t>
+          <t>176518; 214951</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>689538; 738597</t>
+          <t>692115; 737936</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>884572; 918467</t>
+          <t>886523; 919393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>791295; 838073</t>
+          <t>791620; 840951</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>409924; 482981</t>
+          <t>400997; 461688</t>
         </is>
       </c>
     </row>
